--- a/COMPANIES/BOGOTA/BOGOTA.xlsx
+++ b/COMPANIES/BOGOTA/BOGOTA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3f096dcb67a58783/Documentos/SEBASTIAN/Documentos/HV_HTML/COMPANIES/BOGOTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="11_AD4D2F04E46CFB4ACB3E20021552F57A683EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9937FB4B-CE9C-44E3-8B4B-E7F4E4385A73}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="11_AD4D2F04E46CFB4ACB3E20021552F57A683EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4053A6FE-EE6D-46BF-858E-9D240EF58062}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -326,9 +326,6 @@
     <t>nombre</t>
   </si>
   <si>
-    <t>Banco de Bogotá</t>
-  </si>
-  <si>
     <t>sector</t>
   </si>
   <si>
@@ -471,6 +468,9 @@
   </si>
   <si>
     <t>average_assets</t>
+  </si>
+  <si>
+    <t>Banco de Bogota</t>
   </si>
 </sst>
 </file>
@@ -547,7 +547,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -560,6 +560,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -847,10 +848,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
         <v>10</v>
-      </c>
-      <c r="B1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -858,39 +859,39 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
         <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
         <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -900,7 +901,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F15F927D-1315-473E-9521-E6B3743531EF}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -909,15 +910,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="5">
         <f>+trimestres!B2</f>
@@ -926,7 +927,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="6">
         <f>+trimestres!B3</f>
@@ -935,7 +936,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="6">
         <f>+trimestres!B4</f>
@@ -944,7 +945,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5">
         <f>+trimestres!B5</f>
@@ -953,7 +954,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="5">
         <f>+trimestres!B6</f>
@@ -962,7 +963,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="6">
         <f>+trimestres!B7</f>
@@ -971,21 +972,28 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="B8" s="11">
+        <f>+trimestres!B8</f>
+        <v>129121422000000</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="5">
         <f>+trimestres!B9</f>
         <v>8.0432107269183036E-3</v>
       </c>
     </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E18" s="12"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1000,38 +1008,38 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4">
         <v>268584000000</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>430124000000</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>393286000000</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1">
         <v>1.6307297822997842E-2</v>
@@ -1045,7 +1053,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1">
         <v>1.7955446354029371E-3</v>
@@ -1059,7 +1067,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="9">
         <f>+resultados!B17/resultados!B18</f>
@@ -1076,7 +1084,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2">
         <v>101525475000000</v>
@@ -1090,7 +1098,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="6">
         <f>+resultados!B6/resultados!B5</f>
@@ -1107,7 +1115,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" s="11">
         <f>+resultados!B4</f>
@@ -1124,7 +1132,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="10">
         <f>+resultados!B9/resultados!B19</f>
@@ -1161,24 +1169,24 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="4">
         <v>149583583000000</v>
@@ -1192,7 +1200,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="4">
         <v>16470172000000</v>
@@ -1206,7 +1214,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4">
         <v>129121422000000</v>
@@ -1220,7 +1228,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="4">
         <v>101525475000000</v>
@@ -1234,7 +1242,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4">
         <f>7690350000000+4117157000000</f>
@@ -1251,7 +1259,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="4">
         <v>3262817000000</v>
@@ -1265,7 +1273,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="4">
         <v>2055116000000</v>
@@ -1279,7 +1287,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="5">
         <f>+B7-B8</f>
@@ -1298,7 +1306,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="4">
         <v>1016215000000</v>
@@ -1312,7 +1320,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="5">
         <f>+B9-B10</f>
@@ -1329,7 +1337,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="4">
         <v>268584000000</v>
@@ -1343,7 +1351,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6">
         <f>+B9/B2</f>
@@ -1360,7 +1368,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="6">
         <f>+B10/B9</f>
@@ -1377,7 +1385,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6">
         <f>+B5/B4</f>
@@ -1394,7 +1402,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" s="6">
         <f>+B3/B2</f>
@@ -1411,7 +1419,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="2">
         <v>16411234000000</v>
@@ -1425,7 +1433,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="2">
         <v>105483054000000</v>
@@ -1439,7 +1447,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="2">
         <f>+(150719627000000+B2)/2</f>
@@ -1471,85 +1479,85 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2">
         <v>3553000000</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2">
         <v>4009803000000</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2">
         <v>-269924000000</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2">
         <v>6781641000000</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2">
         <v>58938000000</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2">
         <v>7731000000</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1557,7 +1565,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2">
         <v>19025955000000</v>
@@ -1565,7 +1573,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2">
         <v>41769000000</v>
